--- a/LOV3_HTX_Financial_Statements_SBA.xlsx
+++ b/LOV3_HTX_Financial_Statements_SBA.xlsx
@@ -6486,13 +6486,13 @@
         <v>23989.32</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>11377.89</v>
+        <v>5877.89</v>
       </c>
       <c r="E64" s="9" t="n">
-        <v>46415.23</v>
+        <v>40915.23</v>
       </c>
       <c r="F64" s="10" t="n">
-        <v>0.02423948971351185</v>
+        <v>0.02136721711194734</v>
       </c>
     </row>
     <row r="65">
@@ -6640,13 +6640,13 @@
         <v>70250.84</v>
       </c>
       <c r="D71" s="13" t="n">
-        <v>91621.53</v>
+        <v>86121.53</v>
       </c>
       <c r="E71" s="13" t="n">
-        <v>179117.73</v>
+        <v>173617.73</v>
       </c>
       <c r="F71" s="14" t="n">
-        <v>0.09354089969698726</v>
+        <v>0.09066862709542274</v>
       </c>
     </row>
     <row r="73">
@@ -6696,13 +6696,13 @@
         <v>0</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="E75" s="9" t="n">
-        <v>2489.75</v>
+        <v>7989.75</v>
       </c>
       <c r="F75" s="10" t="n">
-        <v>0.001300225583590045</v>
+        <v>0.004172498185154557</v>
       </c>
     </row>
     <row r="76">
@@ -6740,13 +6740,13 @@
         <v>2342.9</v>
       </c>
       <c r="D77" s="13" t="n">
-        <v>3450</v>
+        <v>8950</v>
       </c>
       <c r="E77" s="13" t="n">
-        <v>9057.65</v>
+        <v>14557.65</v>
       </c>
       <c r="F77" s="14" t="n">
-        <v>0.004730189078101965</v>
+        <v>0.007602461679666477</v>
       </c>
     </row>
     <row r="79">
@@ -8426,13 +8426,13 @@
         <v>23989.32</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>11377.89</v>
+        <v>5877.89</v>
       </c>
       <c r="H64" s="9" t="n">
-        <v>56188.56</v>
+        <v>50688.56</v>
       </c>
       <c r="I64" s="10" t="n">
-        <v>0.01521778743478883</v>
+        <v>0.01372819896889224</v>
       </c>
     </row>
     <row r="65">
@@ -8643,13 +8643,13 @@
         <v>70250.84</v>
       </c>
       <c r="G71" s="13" t="n">
-        <v>91621.53</v>
+        <v>86121.53</v>
       </c>
       <c r="H71" s="13" t="n">
-        <v>273827.64</v>
+        <v>268327.64</v>
       </c>
       <c r="I71" s="14" t="n">
-        <v>0.07416190803412438</v>
+        <v>0.07267231956822778</v>
       </c>
     </row>
     <row r="73">
@@ -8720,13 +8720,13 @@
         <v>0</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="H75" s="9" t="n">
-        <v>6221.75</v>
+        <v>11721.75</v>
       </c>
       <c r="I75" s="10" t="n">
-        <v>0.001685063097762203</v>
+        <v>0.003174651563658794</v>
       </c>
     </row>
     <row r="76">
@@ -8782,13 +8782,13 @@
         <v>2342.9</v>
       </c>
       <c r="G77" s="13" t="n">
-        <v>3450</v>
+        <v>8950</v>
       </c>
       <c r="H77" s="13" t="n">
-        <v>19777.18</v>
+        <v>25277.18</v>
       </c>
       <c r="I77" s="14" t="n">
-        <v>0.00535633803926559</v>
+        <v>0.006845926505162182</v>
       </c>
     </row>
     <row r="79">
@@ -9084,10 +9084,10 @@
         <v>3732</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>2489.75</v>
+        <v>7989.75</v>
       </c>
       <c r="D15" s="27" t="n">
-        <v>6221.75</v>
+        <v>11721.75</v>
       </c>
     </row>
     <row r="16">
@@ -9116,10 +9116,10 @@
         <v>75540.70999999999</v>
       </c>
       <c r="C17" s="32" t="n">
-        <v>104841.4</v>
+        <v>110341.4</v>
       </c>
       <c r="D17" s="32" t="n">
-        <v>180382.11</v>
+        <v>185882.11</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
@@ -9139,10 +9139,10 @@
         <v>464152.9</v>
       </c>
       <c r="C19" s="34" t="n">
-        <v>371618.64</v>
+        <v>377118.64</v>
       </c>
       <c r="D19" s="34" t="n">
-        <v>835771.54</v>
+        <v>841271.54</v>
       </c>
     </row>
     <row r="20">
@@ -9155,10 +9155,10 @@
         <v>0.2611363654188097</v>
       </c>
       <c r="C20" s="35" t="n">
-        <v>0.1940709159823029</v>
+        <v>0.1969431885838674</v>
       </c>
       <c r="D20" s="35" t="n">
-        <v>0.2263555720197512</v>
+        <v>0.2278451604856478</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
@@ -9178,10 +9178,10 @@
         <v>9773.33</v>
       </c>
       <c r="C22" s="27" t="n">
-        <v>46415.23</v>
+        <v>40915.23</v>
       </c>
       <c r="D22" s="27" t="n">
-        <v>56188.56</v>
+        <v>50688.56</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
